--- a/data-raw/data.input.xlsx
+++ b/data-raw/data.input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/software/r3PG/r3PG/pkg/data-raw/internal_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2B8460-F4DF-E34A-AC68-C45984930525}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A76588E-CED0-B446-AE2B-9A4912E1DC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24800" yWindow="560" windowWidth="25020" windowHeight="28120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="24800" yWindow="560" windowWidth="25020" windowHeight="28120" activeTab="4" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="site" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="153">
   <si>
     <t>pFS2</t>
   </si>
@@ -471,6 +471,24 @@
   </si>
   <si>
     <t>stems_n</t>
+  </si>
+  <si>
+    <t>beta0</t>
+  </si>
+  <si>
+    <t>betaB</t>
+  </si>
+  <si>
+    <t>betaN</t>
+  </si>
+  <si>
+    <t>betafN</t>
+  </si>
+  <si>
+    <t>betafT</t>
+  </si>
+  <si>
+    <t>betafPhys</t>
   </si>
 </sst>
 </file>
@@ -525,13 +543,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -556,9 +573,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -596,7 +613,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -702,7 +719,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -844,7 +861,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -902,7 +919,7 @@
       <c r="A2">
         <v>47.57</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>100</v>
       </c>
       <c r="C2">
@@ -917,10 +934,10 @@
       <c r="F2">
         <v>106</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>141</v>
       </c>
     </row>
@@ -6529,12 +6546,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E9A71-E1A2-2845-B4A9-990606FB2D91}">
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -6555,7 +6572,7 @@
       <c r="B2">
         <v>0.7</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>0.7</v>
       </c>
     </row>
@@ -6566,7 +6583,7 @@
       <c r="B3">
         <v>0.06</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>0.21</v>
       </c>
     </row>
@@ -6577,7 +6594,7 @@
       <c r="B4">
         <v>0.18338848112302766</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>0.1259168645351276</v>
       </c>
     </row>
@@ -6588,7 +6605,7 @@
       <c r="B5">
         <v>2.3895</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>2.2679</v>
       </c>
     </row>
@@ -6599,7 +6616,7 @@
       <c r="B6">
         <v>0.7</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>0.7</v>
       </c>
     </row>
@@ -6610,7 +6627,7 @@
       <c r="B7">
         <v>0.3</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>0.3</v>
       </c>
     </row>
@@ -6621,7 +6638,7 @@
       <c r="B8">
         <v>0.02</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
@@ -6632,7 +6649,7 @@
       <c r="B9">
         <v>1E-3</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>1E-3</v>
       </c>
     </row>
@@ -6643,7 +6660,7 @@
       <c r="B10">
         <v>60</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>60</v>
       </c>
     </row>
@@ -6654,7 +6671,7 @@
       <c r="B11">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
@@ -6665,7 +6682,7 @@
       <c r="B12">
         <v>5</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>0</v>
       </c>
     </row>
@@ -6676,7 +6693,7 @@
       <c r="B13">
         <v>11</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <v>0</v>
       </c>
     </row>
@@ -6687,7 +6704,7 @@
       <c r="B14">
         <v>-5</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14">
         <v>-5</v>
       </c>
     </row>
@@ -6698,7 +6715,7 @@
       <c r="B15">
         <v>20</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <v>15</v>
       </c>
     </row>
@@ -6709,7 +6726,7 @@
       <c r="B16">
         <v>25</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16">
         <v>35</v>
       </c>
     </row>
@@ -6720,7 +6737,7 @@
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17">
         <v>1</v>
       </c>
     </row>
@@ -6731,7 +6748,7 @@
       <c r="B18">
         <v>0.7</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18">
         <v>0.7</v>
       </c>
     </row>
@@ -6742,7 +6759,7 @@
       <c r="B19">
         <v>9</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>9</v>
       </c>
     </row>
@@ -6753,7 +6770,7 @@
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20">
         <v>1</v>
       </c>
     </row>
@@ -6764,7 +6781,7 @@
       <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21">
         <v>1</v>
       </c>
     </row>
@@ -6775,7 +6792,7 @@
       <c r="B22">
         <v>0</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22">
         <v>0</v>
       </c>
     </row>
@@ -6786,7 +6803,7 @@
       <c r="B23">
         <v>0.5</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23">
         <v>0.2</v>
       </c>
     </row>
@@ -6797,7 +6814,7 @@
       <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24">
         <v>1</v>
       </c>
     </row>
@@ -6808,7 +6825,7 @@
       <c r="B25">
         <v>300</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25">
         <v>350</v>
       </c>
     </row>
@@ -6819,7 +6836,7 @@
       <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26">
         <v>4</v>
       </c>
     </row>
@@ -6830,7 +6847,7 @@
       <c r="B27">
         <v>0.95</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27">
         <v>0.95</v>
       </c>
     </row>
@@ -6841,7 +6858,7 @@
       <c r="B28">
         <v>0</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28">
         <v>0</v>
       </c>
     </row>
@@ -6852,7 +6869,7 @@
       <c r="B29">
         <v>0</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29">
         <v>0</v>
       </c>
     </row>
@@ -6863,7 +6880,7 @@
       <c r="B30">
         <v>0</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30">
         <v>0</v>
       </c>
     </row>
@@ -6874,7 +6891,7 @@
       <c r="B31">
         <v>1</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31">
         <v>1</v>
       </c>
     </row>
@@ -6885,7 +6902,7 @@
       <c r="B32">
         <v>400</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32">
         <v>400</v>
       </c>
     </row>
@@ -6896,431 +6913,431 @@
       <c r="B33">
         <v>1.5</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33">
         <v>1.5</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="B35">
-        <v>0.2</v>
-      </c>
-      <c r="C35" s="1">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="B36">
-        <v>0.4</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="B37">
-        <v>24.718999411782914</v>
-      </c>
-      <c r="C37" s="1">
-        <v>4.2920969347823963</v>
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="B38">
-        <v>19.402050203937655</v>
-      </c>
-      <c r="C38" s="1">
-        <v>4.2920969347823963</v>
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="B39">
-        <v>35</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B40">
-        <v>0.41781825591268146</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0.38277020142713869</v>
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B41">
-        <v>10</v>
-      </c>
-      <c r="C41" s="1">
-        <v>10</v>
+        <v>0.2</v>
+      </c>
+      <c r="C41">
+        <v>0.2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B42">
-        <v>0.23733333333333331</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.39457142857142857</v>
+        <v>0.4</v>
+      </c>
+      <c r="C42">
+        <v>0.4</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B43">
-        <v>3</v>
-      </c>
-      <c r="C43" s="1">
-        <v>3</v>
+        <v>24.718999411782914</v>
+      </c>
+      <c r="C43">
+        <v>4.2920969347823963</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B44">
-        <v>5</v>
-      </c>
-      <c r="C44" s="1">
-        <v>5</v>
+        <v>19.402050203937655</v>
+      </c>
+      <c r="C44">
+        <v>4.2920969347823963</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B45">
-        <v>4.9810073254773303E-2</v>
-      </c>
-      <c r="C45" s="1">
-        <v>4.8565574202227367E-2</v>
+        <v>35</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B46">
-        <v>0.47</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0.47</v>
+        <v>0.41781825591268146</v>
+      </c>
+      <c r="C46">
+        <v>0.38277020142713869</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="C47" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B48">
-        <v>0.02</v>
-      </c>
-      <c r="C48" s="1">
-        <v>0.02</v>
+        <v>0.23733333333333331</v>
+      </c>
+      <c r="C48">
+        <v>0.39457142857142857</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B49">
-        <v>3.33</v>
-      </c>
-      <c r="C49" s="1">
-        <v>3.33</v>
+        <v>3</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B50">
-        <v>5.6999999999999995E-2</v>
-      </c>
-      <c r="C50" s="1">
-        <v>0.05</v>
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B51">
-        <v>0.2</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.2</v>
+        <v>4.9810073254773303E-2</v>
+      </c>
+      <c r="C51">
+        <v>4.8565574202227367E-2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B52">
-        <v>0.66</v>
-      </c>
-      <c r="C52" s="1">
-        <v>0.66</v>
+        <v>0.47</v>
+      </c>
+      <c r="C52">
+        <v>0.47</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B53">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B54">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C54" s="1">
-        <v>4.4000000000000004</v>
+        <v>0.02</v>
+      </c>
+      <c r="C54">
+        <v>0.02</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B55">
-        <v>27</v>
-      </c>
-      <c r="C55" s="1">
-        <v>27</v>
+        <v>3.33</v>
+      </c>
+      <c r="C55">
+        <v>3.33</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B56">
-        <v>0.75</v>
-      </c>
-      <c r="C56" s="1">
-        <v>0.75</v>
+        <v>5.6999999999999995E-2</v>
+      </c>
+      <c r="C56">
+        <v>0.05</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B57">
-        <v>0.15</v>
-      </c>
-      <c r="C57" s="1">
-        <v>0.15</v>
+        <v>0.2</v>
+      </c>
+      <c r="C57">
+        <v>0.2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58" s="1">
-        <v>2</v>
+        <v>0.66</v>
+      </c>
+      <c r="C58">
+        <v>0.66</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B59">
-        <v>0.56699999999999995</v>
-      </c>
-      <c r="C59" s="1">
-        <v>0.39500000000000002</v>
+        <v>2</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B60">
-        <v>0.56699999999999995</v>
-      </c>
-      <c r="C60" s="1">
-        <v>0.39500000000000002</v>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C60">
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61" s="1">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="C61">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B62">
-        <v>3</v>
-      </c>
-      <c r="C62" s="1">
-        <v>3</v>
+        <v>0.75</v>
+      </c>
+      <c r="C62">
+        <v>0.75</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B63">
-        <v>1.0079269437862552</v>
+        <v>0.15</v>
       </c>
       <c r="C63">
-        <v>4.588685316132576</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B64">
-        <v>0.53753519999999999</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>0.4738211</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B65">
-        <v>0.44984780000000002</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>0.39500000000000002</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>0.39500000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>1.0079269437862552</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>4.588685316132576</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B70">
-        <v>0.93895242486246377</v>
+        <v>0.53753519999999999</v>
       </c>
       <c r="C70">
-        <v>1.3764906078875401</v>
+        <v>0.4738211</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B71">
-        <v>0.5812155</v>
+        <v>0.44984780000000002</v>
       </c>
       <c r="C71">
-        <v>0.55362769999999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -7331,18 +7348,18 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73">
-        <v>-0.27724310000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -7353,100 +7370,166 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B75">
-        <v>6.2690037344620873</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>2.1885791577597868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B76">
-        <v>0.18916359999999999</v>
+        <v>0.93895242486246377</v>
       </c>
       <c r="C76">
-        <v>0.56325259999999999</v>
+        <v>1.3764906078875401</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>0.5812155</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>0.55362769999999994</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>-0.26567479999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B79">
-        <v>0.6551283</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>0.67789920000000004</v>
+        <v>-0.27724310000000002</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="B80">
-        <v>-90</v>
-      </c>
-      <c r="C80" s="1">
-        <v>-90</v>
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="B81">
-        <v>0.8</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0.8</v>
+        <v>6.2690037344620873</v>
+      </c>
+      <c r="C81">
+        <v>2.1885791577597868</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="B82">
-        <v>24</v>
-      </c>
-      <c r="C82" s="1">
-        <v>24</v>
+        <v>0.18916359999999999</v>
+      </c>
+      <c r="C82">
+        <v>0.56325259999999999</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>77</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>-0.26567479999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>78</v>
+      </c>
+      <c r="B85">
+        <v>0.6551283</v>
+      </c>
+      <c r="C85">
+        <v>0.67789920000000004</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>109</v>
+      </c>
+      <c r="B86">
+        <v>-90</v>
+      </c>
+      <c r="C86">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>110</v>
+      </c>
+      <c r="B87">
+        <v>0.8</v>
+      </c>
+      <c r="C87">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>111</v>
+      </c>
+      <c r="B88">
+        <v>24</v>
+      </c>
+      <c r="C88">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>112</v>
       </c>
-      <c r="B83">
+      <c r="B89">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C89">
         <v>2.2999999999999998</v>
       </c>
     </row>

--- a/data-raw/data.input.xlsx
+++ b/data-raw/data.input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\thinning_defoliation_events\Rdata\data\revised_files_Vova\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A76588E-CED0-B446-AE2B-9A4912E1DC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631610A8-E512-4838-93D7-FAB615476981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24800" yWindow="560" windowWidth="25020" windowHeight="28120" activeTab="4" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="site" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="149">
   <si>
     <t>pFS2</t>
   </si>
@@ -218,12 +218,6 @@
     <t>aH</t>
   </si>
   <si>
-    <t>nHB</t>
-  </si>
-  <si>
-    <t>nHC</t>
-  </si>
-  <si>
     <t>aV</t>
   </si>
   <si>
@@ -242,33 +236,9 @@
     <t>aK</t>
   </si>
   <si>
-    <t>nKB</t>
-  </si>
-  <si>
-    <t>nKH</t>
-  </si>
-  <si>
-    <t>nKC</t>
-  </si>
-  <si>
-    <t>nKrh</t>
-  </si>
-  <si>
     <t>aHL</t>
   </si>
   <si>
-    <t>nHLB</t>
-  </si>
-  <si>
-    <t>nHLL</t>
-  </si>
-  <si>
-    <t>nHLC</t>
-  </si>
-  <si>
-    <t>nHLrh</t>
-  </si>
-  <si>
     <t>Dscale0</t>
   </si>
   <si>
@@ -314,51 +284,6 @@
     <t>DlocationC</t>
   </si>
   <si>
-    <t>wsscale0</t>
-  </si>
-  <si>
-    <t>wsscaleB</t>
-  </si>
-  <si>
-    <t>wsscalerh</t>
-  </si>
-  <si>
-    <t>wsscalet</t>
-  </si>
-  <si>
-    <t>wsscaleC</t>
-  </si>
-  <si>
-    <t>wsshape0</t>
-  </si>
-  <si>
-    <t>wsshapeB</t>
-  </si>
-  <si>
-    <t>wsshaperh</t>
-  </si>
-  <si>
-    <t>wsshapet</t>
-  </si>
-  <si>
-    <t>wsshapeC</t>
-  </si>
-  <si>
-    <t>wslocation0</t>
-  </si>
-  <si>
-    <t>wslocationB</t>
-  </si>
-  <si>
-    <t>wslocationrh</t>
-  </si>
-  <si>
-    <t>wslocationt</t>
-  </si>
-  <si>
-    <t>wslocationC</t>
-  </si>
-  <si>
     <t>Qa</t>
   </si>
   <si>
@@ -395,9 +320,6 @@
     <t>asw_max</t>
   </si>
   <si>
-    <t>altitude</t>
-  </si>
-  <si>
     <t>species</t>
   </si>
   <si>
@@ -489,6 +411,72 @@
   </si>
   <si>
     <t>betafPhys</t>
+  </si>
+  <si>
+    <t>elevation</t>
+  </si>
+  <si>
+    <t>lt_mod_mths</t>
+  </si>
+  <si>
+    <t>st_Power</t>
+  </si>
+  <si>
+    <t>st_Intercept</t>
+  </si>
+  <si>
+    <t>st_fN</t>
+  </si>
+  <si>
+    <t>st_fT</t>
+  </si>
+  <si>
+    <t>st_fPhys</t>
+  </si>
+  <si>
+    <t>biom_prop_retained</t>
+  </si>
+  <si>
+    <t>gammaAPAR</t>
+  </si>
+  <si>
+    <t>Hd</t>
+  </si>
+  <si>
+    <t>nH1</t>
+  </si>
+  <si>
+    <t>nH2</t>
+  </si>
+  <si>
+    <t>nH3</t>
+  </si>
+  <si>
+    <t>nH4</t>
+  </si>
+  <si>
+    <t>nK1</t>
+  </si>
+  <si>
+    <t>nK2</t>
+  </si>
+  <si>
+    <t>nK3</t>
+  </si>
+  <si>
+    <t>nK4</t>
+  </si>
+  <si>
+    <t>nHL1</t>
+  </si>
+  <si>
+    <t>nHL2</t>
+  </si>
+  <si>
+    <t>nHL3</t>
+  </si>
+  <si>
+    <t>nHL4</t>
   </si>
 </sst>
 </file>
@@ -543,7 +531,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -554,6 +542,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -869,53 +858,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACAC9B12-40B2-9A4C-94F4-5F3D5BCCC889}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O1" t="s">
         <v>121</v>
       </c>
-      <c r="C1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="P1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>47.57</v>
       </c>
@@ -935,54 +960,94 @@
         <v>106</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>141</v>
+        <v>115</v>
+      </c>
+      <c r="I2">
+        <v>120</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>-15.9246784369849</v>
+      </c>
+      <c r="P2">
+        <v>1.0516235132282401</v>
+      </c>
+      <c r="Q2">
+        <v>2.1819192598143098</v>
+      </c>
+      <c r="R2">
+        <v>-1.3467926298486801</v>
+      </c>
+      <c r="S2">
+        <v>-1.5757229739474199</v>
+      </c>
+      <c r="T2">
+        <v>-2.1528301145871098</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9C5410-71A4-1341-9BA7-8401CA4E6F0A}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="E1" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="F1" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="G1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C2">
         <v>0.5</v>
@@ -1000,12 +1065,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C3">
         <v>0.5</v>
@@ -1025,47 +1090,51 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E86F09-F9D3-4B49-968A-3E0A41AAD9D8}">
   <dimension ref="A1:J169"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="D1" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="E1" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="F1" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G1" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="H1" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="I1" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="J1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2001</v>
       </c>
@@ -1097,7 +1166,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2001</v>
       </c>
@@ -1129,7 +1198,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -1161,7 +1230,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2001</v>
       </c>
@@ -1193,7 +1262,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2001</v>
       </c>
@@ -1225,7 +1294,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2001</v>
       </c>
@@ -1257,7 +1326,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2001</v>
       </c>
@@ -1289,7 +1358,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2001</v>
       </c>
@@ -1321,7 +1390,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2001</v>
       </c>
@@ -1353,7 +1422,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2001</v>
       </c>
@@ -1385,7 +1454,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2001</v>
       </c>
@@ -1417,7 +1486,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2001</v>
       </c>
@@ -1449,7 +1518,7 @@
         <v>-7.6778263499915012</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2002</v>
       </c>
@@ -1481,7 +1550,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2002</v>
       </c>
@@ -1513,7 +1582,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2002</v>
       </c>
@@ -1545,7 +1614,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2002</v>
       </c>
@@ -1577,7 +1646,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2002</v>
       </c>
@@ -1609,7 +1678,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2002</v>
       </c>
@@ -1641,7 +1710,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2002</v>
       </c>
@@ -1673,7 +1742,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2002</v>
       </c>
@@ -1705,7 +1774,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2002</v>
       </c>
@@ -1737,7 +1806,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2002</v>
       </c>
@@ -1769,7 +1838,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2002</v>
       </c>
@@ -1801,7 +1870,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2002</v>
       </c>
@@ -1833,7 +1902,7 @@
         <v>-7.7052220501109474</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2003</v>
       </c>
@@ -1865,7 +1934,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2003</v>
       </c>
@@ -1897,7 +1966,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2003</v>
       </c>
@@ -1929,7 +1998,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2003</v>
       </c>
@@ -1961,7 +2030,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2003</v>
       </c>
@@ -1993,7 +2062,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2003</v>
       </c>
@@ -2025,7 +2094,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2003</v>
       </c>
@@ -2057,7 +2126,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2003</v>
       </c>
@@ -2089,7 +2158,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2003</v>
       </c>
@@ -2121,7 +2190,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2003</v>
       </c>
@@ -2153,7 +2222,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2003</v>
       </c>
@@ -2185,7 +2254,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2003</v>
       </c>
@@ -2217,7 +2286,7 @@
         <v>-7.7332187340141187</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2004</v>
       </c>
@@ -2249,7 +2318,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2004</v>
       </c>
@@ -2281,7 +2350,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2004</v>
       </c>
@@ -2313,7 +2382,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2004</v>
       </c>
@@ -2345,7 +2414,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2004</v>
       </c>
@@ -2377,7 +2446,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2004</v>
       </c>
@@ -2409,7 +2478,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2004</v>
       </c>
@@ -2441,7 +2510,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2004</v>
       </c>
@@ -2473,7 +2542,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2004</v>
       </c>
@@ -2505,7 +2574,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2004</v>
       </c>
@@ -2537,7 +2606,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2004</v>
       </c>
@@ -2569,7 +2638,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2004</v>
       </c>
@@ -2601,7 +2670,7 @@
         <v>-7.7618295855768338</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2005</v>
       </c>
@@ -2633,7 +2702,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2005</v>
       </c>
@@ -2665,7 +2734,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2005</v>
       </c>
@@ -2697,7 +2766,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2005</v>
       </c>
@@ -2729,7 +2798,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2005</v>
       </c>
@@ -2761,7 +2830,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2005</v>
       </c>
@@ -2793,7 +2862,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2005</v>
       </c>
@@ -2825,7 +2894,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2005</v>
       </c>
@@ -2857,7 +2926,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2005</v>
       </c>
@@ -2889,7 +2958,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2005</v>
       </c>
@@ -2921,7 +2990,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2005</v>
       </c>
@@ -2953,7 +3022,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2005</v>
       </c>
@@ -2985,7 +3054,7 @@
         <v>-7.7910680778916674</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2006</v>
       </c>
@@ -3017,7 +3086,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2006</v>
       </c>
@@ -3049,7 +3118,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2006</v>
       </c>
@@ -3081,7 +3150,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2006</v>
       </c>
@@ -3113,7 +3182,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2006</v>
       </c>
@@ -3145,7 +3214,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2006</v>
       </c>
@@ -3177,7 +3246,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2006</v>
       </c>
@@ -3209,7 +3278,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2006</v>
       </c>
@@ -3241,7 +3310,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2006</v>
       </c>
@@ -3273,7 +3342,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2006</v>
       </c>
@@ -3305,7 +3374,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2006</v>
       </c>
@@ -3337,7 +3406,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2006</v>
       </c>
@@ -3369,7 +3438,7 @@
         <v>-7.820947979612547</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2007</v>
       </c>
@@ -3401,7 +3470,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2007</v>
       </c>
@@ -3433,7 +3502,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2007</v>
       </c>
@@ -3465,7 +3534,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2007</v>
       </c>
@@ -3497,7 +3566,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2007</v>
       </c>
@@ -3529,7 +3598,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2007</v>
       </c>
@@ -3561,7 +3630,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2007</v>
       </c>
@@ -3593,7 +3662,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2007</v>
       </c>
@@ -3625,7 +3694,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2007</v>
       </c>
@@ -3657,7 +3726,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2007</v>
       </c>
@@ -3689,7 +3758,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2007</v>
       </c>
@@ -3721,7 +3790,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2007</v>
       </c>
@@ -3753,7 +3822,7 @@
         <v>-7.8514833614385262</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2008</v>
       </c>
@@ -3785,7 +3854,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2008</v>
       </c>
@@ -3817,7 +3886,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2008</v>
       </c>
@@ -3849,7 +3918,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2008</v>
       </c>
@@ -3881,7 +3950,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2008</v>
       </c>
@@ -3913,7 +3982,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2008</v>
       </c>
@@ -3945,7 +4014,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2008</v>
       </c>
@@ -3977,7 +4046,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2008</v>
       </c>
@@ -4009,7 +4078,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2008</v>
       </c>
@@ -4041,7 +4110,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2008</v>
       </c>
@@ -4073,7 +4142,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2008</v>
       </c>
@@ -4105,7 +4174,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2008</v>
       </c>
@@ -4137,7 +4206,7 @@
         <v>-7.8826886027397975</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2009</v>
       </c>
@@ -4169,7 +4238,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2009</v>
       </c>
@@ -4201,7 +4270,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2009</v>
       </c>
@@ -4233,7 +4302,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2009</v>
       </c>
@@ -4265,7 +4334,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2009</v>
       </c>
@@ -4297,7 +4366,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2009</v>
       </c>
@@ -4329,7 +4398,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2009</v>
       </c>
@@ -4361,7 +4430,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2009</v>
       </c>
@@ -4393,7 +4462,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2009</v>
       </c>
@@ -4425,7 +4494,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2009</v>
       </c>
@@ -4457,7 +4526,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2009</v>
       </c>
@@ -4489,7 +4558,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2009</v>
       </c>
@@ -4521,7 +4590,7 @@
         <v>-7.9145783983290627</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2010</v>
       </c>
@@ -4553,7 +4622,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2010</v>
       </c>
@@ -4585,7 +4654,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2010</v>
       </c>
@@ -4617,7 +4686,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2010</v>
       </c>
@@ -4649,7 +4718,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2010</v>
       </c>
@@ -4681,7 +4750,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2010</v>
       </c>
@@ -4713,7 +4782,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2010</v>
       </c>
@@ -4745,7 +4814,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2010</v>
       </c>
@@ -4777,7 +4846,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2010</v>
       </c>
@@ -4809,7 +4878,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2010</v>
       </c>
@@ -4841,7 +4910,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2010</v>
       </c>
@@ -4873,7 +4942,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2010</v>
       </c>
@@ -4905,7 +4974,7 @@
         <v>-7.9471677653814368</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2011</v>
       </c>
@@ -4937,7 +5006,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2011</v>
       </c>
@@ -4969,7 +5038,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2011</v>
       </c>
@@ -5001,7 +5070,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2011</v>
       </c>
@@ -5033,7 +5102,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2011</v>
       </c>
@@ -5065,7 +5134,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2011</v>
       </c>
@@ -5097,7 +5166,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2011</v>
       </c>
@@ -5129,7 +5198,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2011</v>
       </c>
@@ -5161,7 +5230,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2011</v>
       </c>
@@ -5193,7 +5262,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2011</v>
       </c>
@@ -5225,7 +5294,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2011</v>
       </c>
@@ -5257,7 +5326,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2011</v>
       </c>
@@ -5289,7 +5358,7 @@
         <v>-7.9804720505061724</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2012</v>
       </c>
@@ -5321,7 +5390,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2012</v>
       </c>
@@ -5353,7 +5422,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2012</v>
       </c>
@@ -5385,7 +5454,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2012</v>
       </c>
@@ -5417,7 +5486,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2012</v>
       </c>
@@ -5449,7 +5518,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2012</v>
       </c>
@@ -5481,7 +5550,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2012</v>
       </c>
@@ -5513,7 +5582,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2012</v>
       </c>
@@ -5545,7 +5614,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2012</v>
       </c>
@@ -5577,7 +5646,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2012</v>
       </c>
@@ -5609,7 +5678,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2012</v>
       </c>
@@ -5641,7 +5710,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2012</v>
       </c>
@@ -5673,7 +5742,7 @@
         <v>-8.0145069369735005</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2013</v>
       </c>
@@ -5705,7 +5774,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2013</v>
       </c>
@@ -5737,7 +5806,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2013</v>
       </c>
@@ -5769,7 +5838,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2013</v>
       </c>
@@ -5801,7 +5870,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2013</v>
       </c>
@@ -5833,7 +5902,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2013</v>
       </c>
@@ -5865,7 +5934,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2013</v>
       </c>
@@ -5897,7 +5966,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2013</v>
       </c>
@@ -5929,7 +5998,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2013</v>
       </c>
@@ -5961,7 +6030,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2013</v>
       </c>
@@ -5993,7 +6062,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2013</v>
       </c>
@@ -6025,7 +6094,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2013</v>
       </c>
@@ -6057,7 +6126,7 @@
         <v>-8.0492884521000221</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2014</v>
       </c>
@@ -6089,7 +6158,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2014</v>
       </c>
@@ -6121,7 +6190,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2014</v>
       </c>
@@ -6153,7 +6222,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2014</v>
       </c>
@@ -6185,7 +6254,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2014</v>
       </c>
@@ -6217,7 +6286,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2014</v>
       </c>
@@ -6249,7 +6318,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2014</v>
       </c>
@@ -6281,7 +6350,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2014</v>
       </c>
@@ -6313,7 +6382,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2014</v>
       </c>
@@ -6345,7 +6414,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2014</v>
       </c>
@@ -6377,7 +6446,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2014</v>
       </c>
@@ -6409,7 +6478,7 @@
         <v>-8.0848329747961003</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2014</v>
       </c>
@@ -6443,45 +6512,52 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3ED633-EED0-A541-B1D7-08B1459B1DF2}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.375" customWidth="1"/>
+    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="E1" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="F1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+      <c r="G1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>48</v>
@@ -6499,9 +6575,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="B3">
         <v>47</v>
@@ -6519,9 +6595,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="B4">
         <v>50</v>
@@ -6541,31 +6617,36 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003E9A71-E1A2-2845-B4A9-990606FB2D91}">
-  <dimension ref="A1:C89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F87"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
         <v>113</v>
       </c>
-      <c r="C1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6576,7 +6657,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6587,7 +6668,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -6598,7 +6679,7 @@
         <v>0.1259168645351276</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6609,7 +6690,7 @@
         <v>2.2679</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -6620,7 +6701,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6631,7 +6712,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6642,7 +6723,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6653,7 +6734,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6664,7 +6745,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6675,7 +6756,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6686,7 +6767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -6697,7 +6778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -6708,7 +6789,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -6719,7 +6800,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -6730,7 +6811,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -6741,7 +6822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -6752,7 +6833,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -6763,7 +6844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -6774,7 +6855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -6785,7 +6866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -6796,7 +6877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -6807,7 +6888,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -6818,7 +6899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -6829,7 +6910,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -6840,7 +6921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -6851,7 +6932,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -6862,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -6873,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -6884,7 +6965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -6895,7 +6976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -6906,7 +6987,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -6917,9 +6998,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6928,273 +7009,273 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>24.718999411782914</v>
       </c>
       <c r="C37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>4.2920969347823963</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>19.402050203937655</v>
       </c>
       <c r="C38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>4.2920969347823963</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>0.41781825591268146</v>
       </c>
       <c r="C40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41">
+        <v>0.38277020142713869</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="4">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>10</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.23733333333333331</v>
+      </c>
+      <c r="C43">
+        <v>0.39457142857142857</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>5</v>
+      </c>
+      <c r="C45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>4.9810073254773303E-2</v>
+      </c>
+      <c r="C46">
+        <v>4.8565574202227367E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.47</v>
+      </c>
+      <c r="C47">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.02</v>
+      </c>
+      <c r="C49">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>3.33</v>
+      </c>
+      <c r="C50">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>5.6999999999999995E-2</v>
+      </c>
+      <c r="C51">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52">
         <v>0.2</v>
       </c>
-      <c r="C41">
+      <c r="C52">
         <v>0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42">
-        <v>0.4</v>
-      </c>
-      <c r="C42">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43">
-        <v>24.718999411782914</v>
-      </c>
-      <c r="C43">
-        <v>4.2920969347823963</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44">
-        <v>19.402050203937655</v>
-      </c>
-      <c r="C44">
-        <v>4.2920969347823963</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45">
-        <v>35</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46">
-        <v>0.41781825591268146</v>
-      </c>
-      <c r="C46">
-        <v>0.38277020142713869</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47">
-        <v>10</v>
-      </c>
-      <c r="C47">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48">
-        <v>0.23733333333333331</v>
-      </c>
-      <c r="C48">
-        <v>0.39457142857142857</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49">
-        <v>3</v>
-      </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50">
-        <v>5</v>
-      </c>
-      <c r="C50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51">
-        <v>4.9810073254773303E-2</v>
-      </c>
-      <c r="C51">
-        <v>4.8565574202227367E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52">
-        <v>0.47</v>
-      </c>
-      <c r="C52">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="C53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B54">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B55">
-        <v>3.33</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="C55">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B56">
-        <v>5.6999999999999995E-2</v>
+        <v>27</v>
       </c>
       <c r="C56">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B57">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="C57">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B58">
-        <v>0.66</v>
+        <v>0.15</v>
       </c>
       <c r="C58">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -7203,360 +7284,342 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B60">
-        <v>4.4000000000000004</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="C60">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.39500000000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B61">
-        <v>27</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="C61">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+        <v>0.39500000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B62">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B63">
-        <v>0.15</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>58</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B64" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="C64" s="4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="B65">
-        <v>0.56699999999999995</v>
+        <v>1.0079269437862552</v>
       </c>
       <c r="C65">
-        <v>0.39500000000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>59</v>
+        <v>4.588685316132576</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="B66">
-        <v>0.56699999999999995</v>
+        <v>0.53753519999999999</v>
       </c>
       <c r="C66">
-        <v>0.39500000000000002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>60</v>
+        <v>0.4738211</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>0.44984780000000002</v>
       </c>
       <c r="C67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74">
+        <v>0.93895242486246377</v>
+      </c>
+      <c r="C74">
+        <v>1.3764906078875401</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75">
+        <v>0.5812155</v>
+      </c>
+      <c r="C75">
+        <v>0.55362769999999994</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>-0.27724310000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B68">
-        <v>3</v>
-      </c>
-      <c r="C68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69">
-        <v>1.0079269437862552</v>
-      </c>
-      <c r="C69">
-        <v>4.588685316132576</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70">
-        <v>0.53753519999999999</v>
-      </c>
-      <c r="C70">
-        <v>0.4738211</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71">
-        <v>0.44984780000000002</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>64</v>
-      </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>66</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>67</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>69</v>
-      </c>
-      <c r="B76">
-        <v>0.93895242486246377</v>
-      </c>
-      <c r="C76">
-        <v>1.3764906078875401</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>70</v>
-      </c>
-      <c r="B77">
-        <v>0.5812155</v>
-      </c>
-      <c r="C77">
-        <v>0.55362769999999994</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>71</v>
-      </c>
-      <c r="B78">
-        <v>0</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>72</v>
-      </c>
       <c r="B79">
-        <v>0</v>
+        <v>6.2690037344620873</v>
       </c>
       <c r="C79">
-        <v>-0.27724310000000002</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>73</v>
+        <v>2.1885791577597868</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>0.18916359999999999</v>
       </c>
       <c r="C80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>74</v>
+        <v>0.56325259999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="B81">
-        <v>6.2690037344620873</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>2.1885791577597868</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>75</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="B82">
-        <v>0.18916359999999999</v>
+        <v>0</v>
       </c>
       <c r="C82">
-        <v>0.56325259999999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>76</v>
+        <v>-0.26567479999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>0.6551283</v>
       </c>
       <c r="C83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>77</v>
+        <v>0.67789920000000004</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="C84">
-        <v>-0.26567479999999999</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>78</v>
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="B85">
-        <v>0.6551283</v>
+        <v>0.8</v>
       </c>
       <c r="C85">
-        <v>0.67789920000000004</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>109</v>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="B86">
-        <v>-90</v>
+        <v>24</v>
       </c>
       <c r="C86">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>110</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="B87">
-        <v>0.8</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="C87">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>111</v>
-      </c>
-      <c r="B88">
-        <v>24</v>
-      </c>
-      <c r="C88">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>112</v>
-      </c>
-      <c r="B89">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C89">
         <v>2.2999999999999998</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AB4F449-9DC8-E74B-BCC1-554BB33610F9}">
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
         <v>113</v>
       </c>
-      <c r="C1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B2">
         <v>0.19438798391558637</v>
@@ -7565,9 +7628,9 @@
         <v>0.27800157495549827</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>1.2246192</v>
@@ -7576,9 +7639,9 @@
         <v>1.1518027</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7587,9 +7650,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B5">
         <v>0.12776940000000001</v>
@@ -7598,9 +7661,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7609,9 +7672,9 @@
         <v>5.4277699999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B7">
         <v>0.78810101950457778</v>
@@ -7620,9 +7683,9 @@
         <v>1.2283156000459392</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B8">
         <v>0.31619239999999998</v>
@@ -7631,9 +7694,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>1.6142477</v>
@@ -7642,9 +7705,9 @@
         <v>1.1889634</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -7653,9 +7716,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B11">
         <v>-0.11702410000000001</v>
@@ -7664,9 +7727,9 @@
         <v>0.2143678</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B12">
         <v>1.6360918833167544</v>
@@ -7675,9 +7738,9 @@
         <v>0.98723714491917658</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B13">
         <v>0.50466180000000005</v>
@@ -7686,9 +7749,9 @@
         <v>0.87204890000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B14">
         <v>-0.62634160000000005</v>
@@ -7697,9 +7760,9 @@
         <v>2.25852E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -7708,9 +7771,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B16">
         <v>4.5786399999999998E-2</v>
@@ -7719,172 +7782,11 @@
         <v>-0.10617219999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17">
-        <v>2.2094402126214635E-2</v>
-      </c>
-      <c r="C17">
-        <v>9.0008110144060058E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18">
-        <v>2.6048110000000002</v>
-      </c>
-      <c r="C18">
-        <v>2.0841154999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19">
-        <v>-1.8148740000000001</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20">
-        <v>0.32097799999999999</v>
-      </c>
-      <c r="C20">
-        <v>0.27149630000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21">
-        <v>8.9823E-2</v>
-      </c>
-      <c r="C21">
-        <v>-0.1222255</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>99</v>
-      </c>
-      <c r="B22">
-        <v>0.64586569454210141</v>
-      </c>
-      <c r="C22">
-        <v>1.1339352444324555</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23">
-        <v>0.26870719999999998</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24">
-        <v>1.7403652999999999</v>
-      </c>
-      <c r="C24">
-        <v>0.94494829999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26">
-        <v>-0.14293220000000001</v>
-      </c>
-      <c r="C26">
-        <v>0.12202789999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27">
-        <v>0.14272679508242667</v>
-      </c>
-      <c r="C27">
-        <v>0.22778889000228159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>105</v>
-      </c>
-      <c r="B28">
-        <v>1.028025</v>
-      </c>
-      <c r="C28">
-        <v>2.203662</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29">
-        <v>-3.4997509999999998</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30">
-        <v>0.453181</v>
-      </c>
-      <c r="C30">
-        <v>-0.41872100000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>108</v>
-      </c>
-      <c r="B31">
-        <v>0.20796600000000001</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>